--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A792C736-9785-417E-9C1C-AF8AC46F0D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ACD614-25AD-4AD5-BBE8-6C4C766C5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -197,14 +197,14 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -213,17 +213,7 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color theme="4" tint="0.39994506668294322"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -321,36 +311,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.39994506668294322"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -699,67 +659,67 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="4">
         <v>45919</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4">
         <v>45926</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4">
         <v>45933</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2">
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4">
         <v>45940</v>
       </c>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2">
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4">
         <v>45947</v>
       </c>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2">
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4">
         <v>45954</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2">
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4">
         <v>45961</v>
       </c>
       <c r="BA1" s="3"/>
@@ -769,7 +729,7 @@
       <c r="BE1" s="3"/>
       <c r="BF1" s="3"/>
       <c r="BG1" s="3"/>
-      <c r="BH1" s="2">
+      <c r="BH1" s="4">
         <v>45975</v>
       </c>
       <c r="BI1" s="3"/>
@@ -779,7 +739,7 @@
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3"/>
-      <c r="BP1" s="2">
+      <c r="BP1" s="4">
         <v>45982</v>
       </c>
       <c r="BQ1" s="3"/>
@@ -789,7 +749,7 @@
       <c r="BU1" s="3"/>
       <c r="BV1" s="3"/>
       <c r="BW1" s="3"/>
-      <c r="BX1" s="2">
+      <c r="BX1" s="4">
         <v>45989</v>
       </c>
       <c r="BY1" s="3"/>
@@ -799,7 +759,7 @@
       <c r="CC1" s="3"/>
       <c r="CD1" s="3"/>
       <c r="CE1" s="3"/>
-      <c r="CF1" s="2">
+      <c r="CF1" s="4">
         <v>45996</v>
       </c>
       <c r="CG1" s="3"/>
@@ -809,7 +769,7 @@
       <c r="CK1" s="3"/>
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
-      <c r="CN1" s="2">
+      <c r="CN1" s="4">
         <v>46003</v>
       </c>
       <c r="CO1" s="3"/>
@@ -1162,7 +1122,7 @@
       </c>
     </row>
     <row r="3" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1177,9 +1137,9 @@
       </c>
     </row>
     <row r="4" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="2"/>
       <c r="C4">
-        <f t="shared" ref="C4:C55" si="0">COUNTIFS(D4:CV4,"x")</f>
+        <f t="shared" ref="C4:C54" si="0">COUNTIFS(D4:CV4,"x")</f>
         <v>0</v>
       </c>
       <c r="D4" t="s">
@@ -1187,7 +1147,7 @@
       </c>
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="2"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1203,7 +1163,7 @@
       </c>
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="2"/>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1216,7 +1176,7 @@
       </c>
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1232,7 +1192,7 @@
       </c>
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="2"/>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1245,7 +1205,7 @@
       </c>
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>37</v>
       </c>
@@ -1270,7 +1230,7 @@
       </c>
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="2"/>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1813,7 +1773,7 @@
       </c>
     </row>
     <row r="40" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B40" t="s">
@@ -1834,14 +1794,14 @@
       </c>
     </row>
     <row r="41" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
+      <c r="A41" s="2"/>
       <c r="C41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="2"/>
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -1857,14 +1817,14 @@
       </c>
     </row>
     <row r="43" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
+      <c r="A43" s="2"/>
       <c r="C43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="2"/>
       <c r="B44" t="s">
         <v>27</v>
       </c>
@@ -1877,14 +1837,14 @@
       </c>
     </row>
     <row r="45" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="2"/>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="2"/>
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -1900,14 +1860,14 @@
       </c>
     </row>
     <row r="47" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="2"/>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="2"/>
       <c r="B48" t="s">
         <v>28</v>
       </c>
@@ -1923,14 +1883,14 @@
       </c>
     </row>
     <row r="49" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="2"/>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="2"/>
       <c r="B50" t="s">
         <v>29</v>
       </c>
@@ -1946,14 +1906,14 @@
       </c>
     </row>
     <row r="51" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="2"/>
       <c r="C51">
         <f>COUNTIFS(D51:CV51,"x")</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="2"/>
       <c r="B52" t="s">
         <v>30</v>
       </c>
@@ -1990,7 +1950,7 @@
       </c>
     </row>
     <row r="53" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
@@ -2053,14 +2013,14 @@
       </c>
     </row>
     <row r="54" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="2"/>
       <c r="C54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B55" t="s">
@@ -2081,10 +2041,12 @@
       </c>
     </row>
     <row r="56" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AI1"/>
     <mergeCell ref="A40:A52"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="CW1:DE1"/>
@@ -2101,77 +2063,47 @@
     <mergeCell ref="BX1:CE1"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="L1:S1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AI1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:CV10 AL27:AP39 Y23:AF39 BN39:BY39 AE48:BI48 AE50:BP52 AE49:CA49 P15:P39 P12:CV14 P11:AM11 M11:O40 S15:CV16 M41:CV41 D11:I52 M42:AA52 AU11:CV11 CC51:CV51 S17:S40 V40:CV40 AG42:CV42 AL23:CV26 Y17:CV22 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AV35:BE39 AR27:CV28 AR29:AS39 D53:CB53 AV29:CV32 AV34:CV34 AV33:BA33 BD33:CV33 BN35:CV38 CD39:CV39 AE45:CV45 AE47:CV47 AE46:BB46 BH46:CV46 BM48:BO48 BS48:BZ48 CC48:CV49 CD50:CV50 CC52 CN52:CW52 CY52:DB52 CV53:DB53">
-    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="x">
+  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O40 C11:I52 P12:CV14 S15:CV16 P15:P39 Y17:CV22 S17:S40 AL23:CV26 Y23:AF39 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O40 D11:I52 P12:CV14 S15:CV16 P15:P39 Y17:CV22 S17:S40 AL23:CV26 Y23:AF39 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53">
+    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:CV10 AL27:AP39 Y23:AF39 BN39:BY39 AE48:BI48 AE50:BP52 AE49:CA49 P15:P39 P12:CV14 P11:AM11 M11:O40 S15:CV16 M41:CV41 C11:I52 M42:AA52 AU11:CV11 CC51:CV51 S17:S40 V40:CV40 AG42:CV42 AL23:CV26 Y17:CV22 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AV35:BE39 AR27:CV28 AR29:AS39 C53:CB53 AV29:CV32 AV34:CV34 AV33:BA33 BD33:CV33 BN35:CV38 CD39:CV39 AE45:CV45 AE47:CV47 AE46:BB46 BH46:CV46 BM48:BO48 BS48:BZ48 CC48:CV49 CD50:CV50 CC52 CN52:CW52 CY52:DB52 CV53:DB53 C54:CV543">
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
+  <conditionalFormatting sqref="X17">
+    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
+  <conditionalFormatting sqref="BM35">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="4" priority="10" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
+  <conditionalFormatting sqref="CB48">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC55">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC55">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="y">
+  <conditionalFormatting sqref="DC55:DE55">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DD55">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",DD55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DD55">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",DD55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE55">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",DE55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DE55">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",DE55)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ACD614-25AD-4AD5-BBE8-6C4C766C5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C90BD2A-07D7-4D47-B5CD-19C98A1E0E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="40">
   <si>
     <t>ATTIVITA</t>
   </si>
@@ -194,26 +194,207 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -659,138 +840,138 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="4">
+      <c r="D1" s="2">
         <v>45919</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2">
         <v>45926</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2">
         <v>45933</v>
       </c>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2">
         <v>45940</v>
       </c>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4">
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2">
         <v>45947</v>
       </c>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4">
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2">
         <v>45954</v>
       </c>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4">
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2">
         <v>45961</v>
       </c>
-      <c r="BA1" s="3"/>
-      <c r="BB1" s="3"/>
-      <c r="BC1" s="3"/>
-      <c r="BD1" s="3"/>
-      <c r="BE1" s="3"/>
-      <c r="BF1" s="3"/>
-      <c r="BG1" s="3"/>
-      <c r="BH1" s="4">
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="2">
         <v>45975</v>
       </c>
-      <c r="BI1" s="3"/>
-      <c r="BJ1" s="3"/>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
-      <c r="BP1" s="4">
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="2">
         <v>45982</v>
       </c>
-      <c r="BQ1" s="3"/>
-      <c r="BR1" s="3"/>
-      <c r="BS1" s="3"/>
-      <c r="BT1" s="3"/>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3"/>
-      <c r="BW1" s="3"/>
-      <c r="BX1" s="4">
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
+      <c r="BT1" s="4"/>
+      <c r="BU1" s="4"/>
+      <c r="BV1" s="4"/>
+      <c r="BW1" s="4"/>
+      <c r="BX1" s="2">
         <v>45989</v>
       </c>
-      <c r="BY1" s="3"/>
-      <c r="BZ1" s="3"/>
-      <c r="CA1" s="3"/>
-      <c r="CB1" s="3"/>
-      <c r="CC1" s="3"/>
-      <c r="CD1" s="3"/>
-      <c r="CE1" s="3"/>
-      <c r="CF1" s="4">
+      <c r="BY1" s="4"/>
+      <c r="BZ1" s="4"/>
+      <c r="CA1" s="4"/>
+      <c r="CB1" s="4"/>
+      <c r="CC1" s="4"/>
+      <c r="CD1" s="4"/>
+      <c r="CE1" s="4"/>
+      <c r="CF1" s="2">
         <v>45996</v>
       </c>
-      <c r="CG1" s="3"/>
-      <c r="CH1" s="3"/>
-      <c r="CI1" s="3"/>
-      <c r="CJ1" s="3"/>
-      <c r="CK1" s="3"/>
-      <c r="CL1" s="3"/>
-      <c r="CM1" s="3"/>
-      <c r="CN1" s="4">
+      <c r="CG1" s="4"/>
+      <c r="CH1" s="4"/>
+      <c r="CI1" s="4"/>
+      <c r="CJ1" s="4"/>
+      <c r="CK1" s="4"/>
+      <c r="CL1" s="4"/>
+      <c r="CM1" s="4"/>
+      <c r="CN1" s="2">
         <v>46003</v>
       </c>
-      <c r="CO1" s="3"/>
-      <c r="CP1" s="3"/>
-      <c r="CQ1" s="3"/>
-      <c r="CR1" s="3"/>
-      <c r="CS1" s="3"/>
-      <c r="CT1" s="3"/>
-      <c r="CU1" s="3"/>
-      <c r="CV1" s="3"/>
-      <c r="CW1" s="3">
+      <c r="CO1" s="4"/>
+      <c r="CP1" s="4"/>
+      <c r="CQ1" s="4"/>
+      <c r="CR1" s="4"/>
+      <c r="CS1" s="4"/>
+      <c r="CT1" s="4"/>
+      <c r="CU1" s="4"/>
+      <c r="CV1" s="4"/>
+      <c r="CW1" s="4">
         <v>19.12</v>
       </c>
-      <c r="CX1" s="3"/>
-      <c r="CY1" s="3"/>
-      <c r="CZ1" s="3"/>
-      <c r="DA1" s="3"/>
-      <c r="DB1" s="3"/>
-      <c r="DC1" s="3"/>
-      <c r="DD1" s="3"/>
-      <c r="DE1" s="3"/>
+      <c r="CX1" s="4"/>
+      <c r="CY1" s="4"/>
+      <c r="CZ1" s="4"/>
+      <c r="DA1" s="4"/>
+      <c r="DB1" s="4"/>
+      <c r="DC1" s="4"/>
+      <c r="DD1" s="4"/>
+      <c r="DE1" s="4"/>
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1122,7 +1303,7 @@
       </c>
     </row>
     <row r="3" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1137,7 +1318,7 @@
       </c>
     </row>
     <row r="4" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
       <c r="C4">
         <f t="shared" ref="C4:C54" si="0">COUNTIFS(D4:CV4,"x")</f>
         <v>0</v>
@@ -1147,7 +1328,7 @@
       </c>
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="3"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1163,7 +1344,7 @@
       </c>
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="3"/>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1176,7 +1357,7 @@
       </c>
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1373,7 @@
       </c>
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3"/>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1205,7 +1386,7 @@
       </c>
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3"/>
       <c r="B9" t="s">
         <v>37</v>
       </c>
@@ -1230,10 +1411,19 @@
       </c>
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3"/>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.25">
@@ -1283,6 +1473,18 @@
       <c r="C12">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.25">
@@ -1345,6 +1547,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="N16" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
@@ -1386,6 +1603,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="S18" t="s">
+        <v>33</v>
+      </c>
+      <c r="T18" t="s">
+        <v>33</v>
+      </c>
+      <c r="U18" t="s">
+        <v>33</v>
+      </c>
+      <c r="V18" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
@@ -1427,6 +1656,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="W20" t="s">
+        <v>33</v>
+      </c>
+      <c r="X20" t="s">
+        <v>33</v>
+      </c>
       <c r="BN20" s="1"/>
       <c r="BO20" s="1"/>
       <c r="BP20" s="1"/>
@@ -1465,6 +1700,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="Y22" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -1488,6 +1735,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AB24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>33</v>
+      </c>
       <c r="CG24" s="1"/>
       <c r="CH24" s="1"/>
       <c r="CI24" s="1"/>
@@ -1518,6 +1777,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AE26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
@@ -1544,6 +1809,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AF28" s="6"/>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
@@ -1773,7 +2039,7 @@
       </c>
     </row>
     <row r="40" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B40" t="s">
@@ -1794,14 +2060,14 @@
       </c>
     </row>
     <row r="41" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="3"/>
       <c r="C41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
+      <c r="A42" s="3"/>
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -1817,14 +2083,14 @@
       </c>
     </row>
     <row r="43" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
+      <c r="A43" s="3"/>
       <c r="C43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
+      <c r="A44" s="3"/>
       <c r="B44" t="s">
         <v>27</v>
       </c>
@@ -1837,14 +2103,14 @@
       </c>
     </row>
     <row r="45" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
+      <c r="A45" s="3"/>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
+      <c r="A46" s="3"/>
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -1860,14 +2126,14 @@
       </c>
     </row>
     <row r="47" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
+      <c r="A47" s="3"/>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
+      <c r="A48" s="3"/>
       <c r="B48" t="s">
         <v>28</v>
       </c>
@@ -1883,14 +2149,14 @@
       </c>
     </row>
     <row r="49" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
+      <c r="A49" s="3"/>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
+      <c r="A50" s="3"/>
       <c r="B50" t="s">
         <v>29</v>
       </c>
@@ -1906,14 +2172,14 @@
       </c>
     </row>
     <row r="51" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
+      <c r="A51" s="3"/>
       <c r="C51">
         <f>COUNTIFS(D51:CV51,"x")</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
+      <c r="A52" s="3"/>
       <c r="B52" t="s">
         <v>30</v>
       </c>
@@ -1950,7 +2216,7 @@
       </c>
     </row>
     <row r="53" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
@@ -2013,14 +2279,14 @@
       </c>
     </row>
     <row r="54" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
+      <c r="A54" s="3"/>
       <c r="C54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B55" t="s">
@@ -2041,15 +2307,10 @@
       </c>
     </row>
     <row r="56" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
+      <c r="A56" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="A40:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="CW1:DE1"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="CF1:CM1"/>
     <mergeCell ref="CN1:CV1"/>
@@ -2063,47 +2324,142 @@
     <mergeCell ref="BX1:CE1"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="L1:S1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="A40:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="CW1:DE1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O40 C11:I52 P12:CV14 S15:CV16 P15:P39 Y17:CV22 S17:S40 AL23:CV26 Y23:AF39 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="y">
+  <conditionalFormatting sqref="P11:AM11 AU11:CV11 C11:I52 P12:CV14 S15:CV16 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 C3:CV10 P15:P39 M11:O15 M17:O40 N16:O16 R16 S17:S40 Y17:CV22 Y23:AF39">
+    <cfRule type="containsText" dxfId="27" priority="31" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O40 D11:I52 P12:CV14 S15:CV16 P15:P39 Y17:CV22 S17:S40 AL23:CV26 Y23:AF39 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53">
-    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="x">
+  <conditionalFormatting sqref="P11:AM11 AU11:CV11 D11:I52 P12:CV14 S15:CV16 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 D3:CV10 P15:P39 M11:O15 M17:O40 N16:O16 R16 S17:S40 Y17:CV22 Y23:AF39">
+    <cfRule type="containsText" dxfId="26" priority="32" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="25" priority="29" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="24" priority="30" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="10" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="22" priority="28" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="21" priority="25" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="20" priority="26" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC55:DE55">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L12">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",L12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L12">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",L12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T18">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T18">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U18">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",U18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U18">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",U18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V18">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",V18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V18">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",V18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W20">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W20">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X20">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",X20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X20">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",X20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="XFD22">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="XFD22">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
+      <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C90BD2A-07D7-4D47-B5CD-19C98A1E0E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0112068C-E423-45F2-97FC-F0D549E83E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="40">
   <si>
     <t>ATTIVITA</t>
   </si>
@@ -197,11 +197,12 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -209,7 +210,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -830,148 +830,148 @@
   <cols>
     <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="100" width="3" bestFit="1" customWidth="1"/>
-    <col min="101" max="102" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="103" max="109" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="102" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="103" max="109" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:109" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="4">
         <v>45919</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4">
         <v>45926</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4">
         <v>45933</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2">
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4">
         <v>45940</v>
       </c>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2">
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4">
         <v>45947</v>
       </c>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2">
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4">
         <v>45954</v>
       </c>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2">
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4">
         <v>45961</v>
       </c>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="2">
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="5"/>
+      <c r="BC1" s="5"/>
+      <c r="BD1" s="5"/>
+      <c r="BE1" s="5"/>
+      <c r="BF1" s="5"/>
+      <c r="BG1" s="5"/>
+      <c r="BH1" s="4">
         <v>45975</v>
       </c>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="2">
+      <c r="BI1" s="5"/>
+      <c r="BJ1" s="5"/>
+      <c r="BK1" s="5"/>
+      <c r="BL1" s="5"/>
+      <c r="BM1" s="5"/>
+      <c r="BN1" s="5"/>
+      <c r="BO1" s="5"/>
+      <c r="BP1" s="4">
         <v>45982</v>
       </c>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="2">
+      <c r="BQ1" s="5"/>
+      <c r="BR1" s="5"/>
+      <c r="BS1" s="5"/>
+      <c r="BT1" s="5"/>
+      <c r="BU1" s="5"/>
+      <c r="BV1" s="5"/>
+      <c r="BW1" s="5"/>
+      <c r="BX1" s="4">
         <v>45989</v>
       </c>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="2">
+      <c r="BY1" s="5"/>
+      <c r="BZ1" s="5"/>
+      <c r="CA1" s="5"/>
+      <c r="CB1" s="5"/>
+      <c r="CC1" s="5"/>
+      <c r="CD1" s="5"/>
+      <c r="CE1" s="5"/>
+      <c r="CF1" s="4">
         <v>45996</v>
       </c>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="2">
+      <c r="CG1" s="5"/>
+      <c r="CH1" s="5"/>
+      <c r="CI1" s="5"/>
+      <c r="CJ1" s="5"/>
+      <c r="CK1" s="5"/>
+      <c r="CL1" s="5"/>
+      <c r="CM1" s="5"/>
+      <c r="CN1" s="4">
         <v>46003</v>
       </c>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4">
+      <c r="CO1" s="5"/>
+      <c r="CP1" s="5"/>
+      <c r="CQ1" s="5"/>
+      <c r="CR1" s="5"/>
+      <c r="CS1" s="5"/>
+      <c r="CT1" s="5"/>
+      <c r="CU1" s="5"/>
+      <c r="CV1" s="5"/>
+      <c r="CW1" s="5">
         <v>19.12</v>
       </c>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
+      <c r="CX1" s="5"/>
+      <c r="CY1" s="5"/>
+      <c r="CZ1" s="5"/>
+      <c r="DA1" s="5"/>
+      <c r="DB1" s="5"/>
+      <c r="DC1" s="5"/>
+      <c r="DD1" s="5"/>
+      <c r="DE1" s="5"/>
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1427,7 +1427,7 @@
       </c>
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
@@ -1469,7 +1469,7 @@
       </c>
     </row>
     <row r="12" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="6"/>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1488,7 +1488,7 @@
       </c>
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="6"/>
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -1516,14 +1516,14 @@
       </c>
     </row>
     <row r="14" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+      <c r="A14" s="6"/>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="6"/>
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -1542,7 +1542,7 @@
       </c>
     </row>
     <row r="16" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1564,7 +1564,7 @@
       </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
+      <c r="A17" s="6"/>
       <c r="B17" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1598,7 @@
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="6"/>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1617,7 +1617,7 @@
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
+      <c r="A19" s="6"/>
       <c r="B19" t="s">
         <v>14</v>
       </c>
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="20" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
+      <c r="A20" s="6"/>
       <c r="C20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1667,7 +1667,7 @@
       <c r="BP20" s="1"/>
     </row>
     <row r="21" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
+      <c r="A21" s="6"/>
       <c r="B21" t="s">
         <v>15</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
+      <c r="A22" s="6"/>
       <c r="C22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1714,7 +1714,7 @@
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
+      <c r="A23" s="6"/>
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -1730,7 +1730,7 @@
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="6"/>
       <c r="C24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1745,6 +1745,9 @@
         <v>33</v>
       </c>
       <c r="AE24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF24" t="s">
         <v>33</v>
       </c>
       <c r="CG24" s="1"/>
@@ -1753,7 +1756,7 @@
       <c r="CJ24" s="1"/>
     </row>
     <row r="25" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
+      <c r="A25" s="6"/>
       <c r="B25" t="s">
         <v>34</v>
       </c>
@@ -1772,20 +1775,29 @@
       </c>
     </row>
     <row r="26" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="6"/>
       <c r="C26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE26" t="s">
-        <v>33</v>
-      </c>
       <c r="AF26" t="s">
         <v>33</v>
       </c>
+      <c r="AG26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
+      <c r="A27" s="6"/>
       <c r="B27" t="s">
         <v>17</v>
       </c>
@@ -1804,15 +1816,19 @@
       </c>
     </row>
     <row r="28" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="6"/>
       <c r="C28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="6"/>
+      <c r="AF28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
+      <c r="A29" s="6"/>
       <c r="B29" t="s">
         <v>18</v>
       </c>
@@ -1837,14 +1853,14 @@
       </c>
     </row>
     <row r="30" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
+      <c r="A30" s="6"/>
       <c r="C30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
+      <c r="A31" s="6"/>
       <c r="B31" t="s">
         <v>19</v>
       </c>
@@ -1878,14 +1894,14 @@
       </c>
     </row>
     <row r="32" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
+      <c r="A32" s="6"/>
       <c r="C32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
+      <c r="A33" s="6"/>
       <c r="B33" t="s">
         <v>20</v>
       </c>
@@ -1922,14 +1938,14 @@
       </c>
     </row>
     <row r="34" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
+      <c r="A34" s="6"/>
       <c r="C34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
+      <c r="A35" s="6"/>
       <c r="B35" t="s">
         <v>21</v>
       </c>
@@ -1948,14 +1964,14 @@
       </c>
     </row>
     <row r="36" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
+      <c r="A36" s="6"/>
       <c r="C36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
+      <c r="A37" s="6"/>
       <c r="B37" t="s">
         <v>22</v>
       </c>
@@ -1998,14 +2014,14 @@
       </c>
     </row>
     <row r="38" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
+      <c r="A38" s="6"/>
       <c r="C38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
+      <c r="A39" s="6"/>
       <c r="B39" t="s">
         <v>23</v>
       </c>
@@ -2311,6 +2327,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="CW1:DE1"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="CF1:CM1"/>
     <mergeCell ref="CN1:CV1"/>
@@ -2327,139 +2345,127 @@
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AI1"/>
     <mergeCell ref="A40:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="CW1:DE1"/>
   </mergeCells>
-  <conditionalFormatting sqref="P11:AM11 AU11:CV11 C11:I52 P12:CV14 S15:CV16 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 C3:CV10 P15:P39 M11:O15 M17:O40 N16:O16 R16 S17:S40 Y17:CV22 Y23:AF39">
-    <cfRule type="containsText" dxfId="27" priority="31" operator="containsText" text="y">
+  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 Y23:AF25 Y27:AF39 Y26:AD26 AF26 AI28:AK28">
+    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P11:AM11 AU11:CV11 D11:I52 P12:CV14 S15:CV16 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 D3:CV10 P15:P39 M11:O15 M17:O40 N16:O16 R16 S17:S40 Y17:CV22 Y23:AF39">
-    <cfRule type="containsText" dxfId="26" priority="32" operator="containsText" text="x">
+  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 Y23:AF25 Y27:AF39 Y26:AD26 AF26 AI28:AK28">
+    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12:L12">
+    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q16:R16">
+    <cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="22" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T18:V18">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W20:X20">
+    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="12" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="25" priority="29" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="30" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="16" priority="38" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="15" priority="35" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="28" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="14" priority="36" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="21" priority="25" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="26" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="12" priority="34" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC55:DE55">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="10" priority="28" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K12">
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",L12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",L12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q16">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q16">
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T18">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T18">
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U18">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",U18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U18">
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",U18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V18">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",V18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V18">
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",V18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W20">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W20">
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X20">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",X20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X20">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",X20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="XFD22">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG26">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AG26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG26">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AG26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH26">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AH26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH26">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AH26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AI26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AI26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ26">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
+      <formula>NOT(ISERROR(SEARCH("y",AJ26)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="XFD22">
+  <conditionalFormatting sqref="AJ26">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
+      <formula>NOT(ISERROR(SEARCH("x",AJ26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0112068C-E423-45F2-97FC-F0D549E83E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C39F3F1-48F0-4D44-8C3A-2D3E079192E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="40">
   <si>
     <t>ATTIVITA</t>
   </si>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -840,138 +840,138 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="4">
+      <c r="D1" s="5">
         <v>45919</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5">
         <v>45926</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4">
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5">
         <v>45933</v>
       </c>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4">
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5">
         <v>45940</v>
       </c>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4">
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5">
         <v>45947</v>
       </c>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4">
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5">
         <v>45954</v>
       </c>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4">
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+      <c r="AY1" s="5"/>
+      <c r="AZ1" s="5">
         <v>45961</v>
       </c>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="5"/>
-      <c r="BF1" s="5"/>
-      <c r="BG1" s="5"/>
-      <c r="BH1" s="4">
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="5">
         <v>45975</v>
       </c>
-      <c r="BI1" s="5"/>
-      <c r="BJ1" s="5"/>
-      <c r="BK1" s="5"/>
-      <c r="BL1" s="5"/>
-      <c r="BM1" s="5"/>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
-      <c r="BP1" s="4">
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="5">
         <v>45982</v>
       </c>
-      <c r="BQ1" s="5"/>
-      <c r="BR1" s="5"/>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
-      <c r="BU1" s="5"/>
-      <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
-      <c r="BX1" s="4">
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
+      <c r="BT1" s="4"/>
+      <c r="BU1" s="4"/>
+      <c r="BV1" s="4"/>
+      <c r="BW1" s="4"/>
+      <c r="BX1" s="5">
         <v>45989</v>
       </c>
-      <c r="BY1" s="5"/>
-      <c r="BZ1" s="5"/>
-      <c r="CA1" s="5"/>
-      <c r="CB1" s="5"/>
-      <c r="CC1" s="5"/>
-      <c r="CD1" s="5"/>
-      <c r="CE1" s="5"/>
-      <c r="CF1" s="4">
+      <c r="BY1" s="4"/>
+      <c r="BZ1" s="4"/>
+      <c r="CA1" s="4"/>
+      <c r="CB1" s="4"/>
+      <c r="CC1" s="4"/>
+      <c r="CD1" s="4"/>
+      <c r="CE1" s="4"/>
+      <c r="CF1" s="5">
         <v>45996</v>
       </c>
-      <c r="CG1" s="5"/>
-      <c r="CH1" s="5"/>
-      <c r="CI1" s="5"/>
-      <c r="CJ1" s="5"/>
-      <c r="CK1" s="5"/>
-      <c r="CL1" s="5"/>
-      <c r="CM1" s="5"/>
-      <c r="CN1" s="4">
+      <c r="CG1" s="4"/>
+      <c r="CH1" s="4"/>
+      <c r="CI1" s="4"/>
+      <c r="CJ1" s="4"/>
+      <c r="CK1" s="4"/>
+      <c r="CL1" s="4"/>
+      <c r="CM1" s="4"/>
+      <c r="CN1" s="5">
         <v>46003</v>
       </c>
-      <c r="CO1" s="5"/>
-      <c r="CP1" s="5"/>
-      <c r="CQ1" s="5"/>
-      <c r="CR1" s="5"/>
-      <c r="CS1" s="5"/>
-      <c r="CT1" s="5"/>
-      <c r="CU1" s="5"/>
-      <c r="CV1" s="5"/>
-      <c r="CW1" s="5">
+      <c r="CO1" s="4"/>
+      <c r="CP1" s="4"/>
+      <c r="CQ1" s="4"/>
+      <c r="CR1" s="4"/>
+      <c r="CS1" s="4"/>
+      <c r="CT1" s="4"/>
+      <c r="CU1" s="4"/>
+      <c r="CV1" s="4"/>
+      <c r="CW1" s="4">
         <v>19.12</v>
       </c>
-      <c r="CX1" s="5"/>
-      <c r="CY1" s="5"/>
-      <c r="CZ1" s="5"/>
-      <c r="DA1" s="5"/>
-      <c r="DB1" s="5"/>
-      <c r="DC1" s="5"/>
-      <c r="DD1" s="5"/>
-      <c r="DE1" s="5"/>
+      <c r="CX1" s="4"/>
+      <c r="CY1" s="4"/>
+      <c r="CZ1" s="4"/>
+      <c r="DA1" s="4"/>
+      <c r="DB1" s="4"/>
+      <c r="DC1" s="4"/>
+      <c r="DD1" s="4"/>
+      <c r="DE1" s="4"/>
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1824,8 +1824,12 @@
       <c r="AF28" s="2"/>
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
-      <c r="AL28" s="2"/>
+      <c r="AK28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
@@ -1858,6 +1862,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AL30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="31" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
@@ -1943,6 +1959,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AP34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="35" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
@@ -1969,6 +1991,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AR36" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS36" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT36" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="37" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
@@ -2018,6 +2049,21 @@
       <c r="C38">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="AU38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:89" x14ac:dyDescent="0.25">
@@ -2327,6 +2373,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="A40:A52"/>
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="CW1:DE1"/>
     <mergeCell ref="A55:A56"/>
@@ -2343,129 +2391,125 @@
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="A40:A52"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 Y23:AF25 Y27:AF39 Y26:AD26 AF26 AI28:AK28">
-    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="y">
+  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543">
+    <cfRule type="containsText" dxfId="27" priority="45" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 AL23:CV26 AR27:CV28 AL27:AP39 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 Y23:AF25 Y27:AF39 Y26:AD26 AF26 AI28:AK28">
-    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="x">
+  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53">
+    <cfRule type="containsText" dxfId="26" priority="46" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12:L12">
-    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="25" priority="29" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="24" priority="30" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:R16">
-    <cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="22" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="22" priority="28" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T18:V18">
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W20:X20">
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="12" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="38" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="16" priority="44" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF26:AJ26">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AF26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AF26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="15" priority="35" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="13" priority="41" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="36" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="12" priority="42" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="11" priority="39" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="34" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="10" priority="40" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC55:DE55">
-    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="28" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="8" priority="34" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="XFD22">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG26">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AG26)))</formula>
+  <conditionalFormatting sqref="AQ34">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AQ34)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG26">
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AG26)))</formula>
+  <conditionalFormatting sqref="AQ34">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AQ34)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH26">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AH26)))</formula>
+  <conditionalFormatting sqref="AT36">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AT36)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH26">
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AH26)))</formula>
+  <conditionalFormatting sqref="AT36">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AT36)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI26">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AI26)))</formula>
+  <conditionalFormatting sqref="AU38">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AU38)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI26">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AI26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ26">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AJ26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ26">
+  <conditionalFormatting sqref="AU38">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AJ26)))</formula>
+      <formula>NOT(ISERROR(SEARCH("x",AU38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C39F3F1-48F0-4D44-8C3A-2D3E079192E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F135A1-D7E1-4922-A559-35C50A04AB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="40">
   <si>
     <t>ATTIVITA</t>
   </si>
@@ -165,8 +165,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -194,27 +202,368 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="62">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4" tint="0.39994506668294322"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -840,138 +1189,138 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1" s="3">
         <v>45919</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3">
         <v>45926</v>
       </c>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5">
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3">
         <v>45933</v>
       </c>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5">
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3">
         <v>45940</v>
       </c>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5">
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3">
         <v>45947</v>
       </c>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="5"/>
-      <c r="AO1" s="5"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5">
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="3"/>
+      <c r="AP1" s="3"/>
+      <c r="AQ1" s="3"/>
+      <c r="AR1" s="3">
         <v>45954</v>
       </c>
-      <c r="AS1" s="5"/>
-      <c r="AT1" s="5"/>
-      <c r="AU1" s="5"/>
-      <c r="AV1" s="5"/>
-      <c r="AW1" s="5"/>
-      <c r="AX1" s="5"/>
-      <c r="AY1" s="5"/>
-      <c r="AZ1" s="5">
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
+      <c r="AU1" s="3"/>
+      <c r="AV1" s="3"/>
+      <c r="AW1" s="3"/>
+      <c r="AX1" s="3"/>
+      <c r="AY1" s="3"/>
+      <c r="AZ1" s="3">
         <v>45961</v>
       </c>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="5">
+      <c r="BA1" s="5"/>
+      <c r="BB1" s="5"/>
+      <c r="BC1" s="5"/>
+      <c r="BD1" s="5"/>
+      <c r="BE1" s="5"/>
+      <c r="BF1" s="5"/>
+      <c r="BG1" s="5"/>
+      <c r="BH1" s="3">
         <v>45975</v>
       </c>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="5">
+      <c r="BI1" s="5"/>
+      <c r="BJ1" s="5"/>
+      <c r="BK1" s="5"/>
+      <c r="BL1" s="5"/>
+      <c r="BM1" s="5"/>
+      <c r="BN1" s="5"/>
+      <c r="BO1" s="5"/>
+      <c r="BP1" s="3">
         <v>45982</v>
       </c>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="5">
+      <c r="BQ1" s="5"/>
+      <c r="BR1" s="5"/>
+      <c r="BS1" s="5"/>
+      <c r="BT1" s="5"/>
+      <c r="BU1" s="5"/>
+      <c r="BV1" s="5"/>
+      <c r="BW1" s="5"/>
+      <c r="BX1" s="3">
         <v>45989</v>
       </c>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="5">
+      <c r="BY1" s="5"/>
+      <c r="BZ1" s="5"/>
+      <c r="CA1" s="5"/>
+      <c r="CB1" s="5"/>
+      <c r="CC1" s="5"/>
+      <c r="CD1" s="5"/>
+      <c r="CE1" s="5"/>
+      <c r="CF1" s="3">
         <v>45996</v>
       </c>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="5">
+      <c r="CG1" s="5"/>
+      <c r="CH1" s="5"/>
+      <c r="CI1" s="5"/>
+      <c r="CJ1" s="5"/>
+      <c r="CK1" s="5"/>
+      <c r="CL1" s="5"/>
+      <c r="CM1" s="5"/>
+      <c r="CN1" s="3">
         <v>46003</v>
       </c>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4">
+      <c r="CO1" s="5"/>
+      <c r="CP1" s="5"/>
+      <c r="CQ1" s="5"/>
+      <c r="CR1" s="5"/>
+      <c r="CS1" s="5"/>
+      <c r="CT1" s="5"/>
+      <c r="CU1" s="5"/>
+      <c r="CV1" s="5"/>
+      <c r="CW1" s="5">
         <v>19.12</v>
       </c>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
+      <c r="CX1" s="5"/>
+      <c r="CY1" s="5"/>
+      <c r="CZ1" s="5"/>
+      <c r="DA1" s="5"/>
+      <c r="DB1" s="5"/>
+      <c r="DC1" s="5"/>
+      <c r="DD1" s="5"/>
+      <c r="DE1" s="5"/>
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1303,7 +1652,7 @@
       </c>
     </row>
     <row r="3" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1318,7 +1667,7 @@
       </c>
     </row>
     <row r="4" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="C4">
         <f t="shared" ref="C4:C54" si="0">COUNTIFS(D4:CV4,"x")</f>
         <v>0</v>
@@ -1328,7 +1677,7 @@
       </c>
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1344,7 +1693,7 @@
       </c>
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1357,7 +1706,7 @@
       </c>
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1373,7 +1722,7 @@
       </c>
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1386,7 +1735,7 @@
       </c>
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
       <c r="B9" t="s">
         <v>37</v>
       </c>
@@ -1411,7 +1760,7 @@
       </c>
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4"/>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1521,6 +1870,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="M14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -1547,12 +1908,6 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" t="s">
-        <v>33</v>
-      </c>
       <c r="P16" t="s">
         <v>33</v>
       </c>
@@ -1560,6 +1915,15 @@
         <v>33</v>
       </c>
       <c r="R16" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" t="s">
+        <v>33</v>
+      </c>
+      <c r="T16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI16" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1603,16 +1967,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S18" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" t="s">
-        <v>33</v>
-      </c>
-      <c r="U18" t="s">
-        <v>33</v>
-      </c>
       <c r="V18" t="s">
+        <v>33</v>
+      </c>
+      <c r="W18" t="s">
+        <v>33</v>
+      </c>
+      <c r="X18" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1656,10 +2020,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W20" t="s">
-        <v>33</v>
-      </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA20" t="s">
         <v>33</v>
       </c>
       <c r="BN20" s="1"/>
@@ -1700,16 +2067,25 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y22" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>33</v>
-      </c>
       <c r="AB22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ22" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1735,19 +2111,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB24" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>33</v>
-      </c>
       <c r="AF24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI24" t="s">
         <v>33</v>
       </c>
       <c r="CG24" s="1"/>
@@ -1780,12 +2153,6 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF26" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>33</v>
-      </c>
       <c r="AH26" t="s">
         <v>33</v>
       </c>
@@ -1824,12 +2191,8 @@
       <c r="AF28" s="2"/>
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
-      <c r="AK28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL28" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
@@ -1862,16 +2225,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AL30" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO30" t="s">
+      <c r="AP30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR30" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1915,6 +2275,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="BE32" t="s">
+        <v>33</v>
+      </c>
+      <c r="BF32" t="s">
+        <v>33</v>
+      </c>
+      <c r="BM32" t="s">
+        <v>33</v>
+      </c>
+      <c r="BN32" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
@@ -1959,10 +2331,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AP34" t="s">
-        <v>33</v>
-      </c>
-      <c r="AQ34" t="s">
+      <c r="AR34" s="7"/>
+      <c r="AU34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BJ34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BK34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BL34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BM34" t="s">
+        <v>33</v>
+      </c>
+      <c r="BN34" s="7"/>
+      <c r="BO34" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2065,6 +2457,39 @@
       <c r="AY38" t="s">
         <v>33</v>
       </c>
+      <c r="AZ38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BA38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BB38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BC38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BD38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BF38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BG38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI38" t="s">
+        <v>33</v>
+      </c>
+      <c r="BJ38" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="39" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
@@ -2101,7 +2526,7 @@
       </c>
     </row>
     <row r="40" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B40" t="s">
@@ -2122,14 +2547,14 @@
       </c>
     </row>
     <row r="41" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
+      <c r="A41" s="4"/>
       <c r="C41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
+      <c r="A42" s="4"/>
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -2145,14 +2570,14 @@
       </c>
     </row>
     <row r="43" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
+      <c r="A43" s="4"/>
       <c r="C43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
+      <c r="A44" s="4"/>
       <c r="B44" t="s">
         <v>27</v>
       </c>
@@ -2165,14 +2590,14 @@
       </c>
     </row>
     <row r="45" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
+      <c r="A45" s="4"/>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
+      <c r="A46" s="4"/>
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -2188,14 +2613,14 @@
       </c>
     </row>
     <row r="47" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
+      <c r="A47" s="4"/>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
+      <c r="A48" s="4"/>
       <c r="B48" t="s">
         <v>28</v>
       </c>
@@ -2211,14 +2636,14 @@
       </c>
     </row>
     <row r="49" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
+      <c r="A49" s="4"/>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
+      <c r="A50" s="4"/>
       <c r="B50" t="s">
         <v>29</v>
       </c>
@@ -2234,14 +2659,14 @@
       </c>
     </row>
     <row r="51" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
+      <c r="A51" s="4"/>
       <c r="C51">
         <f>COUNTIFS(D51:CV51,"x")</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
+      <c r="A52" s="4"/>
       <c r="B52" t="s">
         <v>30</v>
       </c>
@@ -2278,7 +2703,7 @@
       </c>
     </row>
     <row r="53" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
@@ -2341,14 +2766,14 @@
       </c>
     </row>
     <row r="54" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
+      <c r="A54" s="4"/>
       <c r="C54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B55" t="s">
@@ -2369,10 +2794,12 @@
       </c>
     </row>
     <row r="56" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
+      <c r="A56" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="L1:S1"/>
+    <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AI1"/>
     <mergeCell ref="A40:A52"/>
     <mergeCell ref="A53:A54"/>
@@ -2389,127 +2816,271 @@
     <mergeCell ref="BP1:BW1"/>
     <mergeCell ref="BX1:CE1"/>
     <mergeCell ref="D1:K1"/>
-    <mergeCell ref="L1:S1"/>
-    <mergeCell ref="T1:AA1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543">
-    <cfRule type="containsText" dxfId="27" priority="45" operator="containsText" text="y">
+  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 P15:P39 N16:O16 Y17:CV17 M17:O40 S17:S40 Y23:AF25 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AV33:BA33 BD33:CV33 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 BF38:BJ38 Y19:CV19 Z18:CV18 AH20:CV20 AL23:CV26 Y21:CV22 S15:CV16 AU34:CV34 AR29:AS39">
+    <cfRule type="containsText" dxfId="61" priority="79" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 Y17:CV22 M17:O40 S17:S40 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AV34:CV34 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53">
-    <cfRule type="containsText" dxfId="26" priority="46" operator="containsText" text="x">
+  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 P15:P39 N16:O16 Y17:CV17 M17:O40 S17:S40 Y23:AF25 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AV33:BA33 BD33:CV33 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 BF38:BJ38 Y19:CV19 Z18:CV18 AH20:CV20 AL23:CV26 Y21:CV22 S15:CV16 AU34:CV34 AR29:AS39">
+    <cfRule type="containsText" dxfId="60" priority="80" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12:L12">
-    <cfRule type="containsText" dxfId="25" priority="29" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="59" priority="63" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="30" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="58" priority="64" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:R16">
-    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="57" priority="61" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="28" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="56" priority="62" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T18:V18">
+  <conditionalFormatting sqref="T18:Y18">
+    <cfRule type="containsText" dxfId="55" priority="55" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="56" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W20:X20">
+    <cfRule type="containsText" dxfId="53" priority="51" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="52" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X17">
+    <cfRule type="containsText" dxfId="51" priority="77" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="50" priority="78" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF26:AG26">
+    <cfRule type="containsText" dxfId="49" priority="41" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AF26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="42" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AF26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ34">
+    <cfRule type="containsText" dxfId="47" priority="39" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AQ34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="40" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AQ34)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT36">
+    <cfRule type="containsText" dxfId="45" priority="37" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AT36)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="38" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AT36)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU38">
+    <cfRule type="containsText" dxfId="43" priority="35" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AU38)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="36" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AU38)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BM35">
+    <cfRule type="containsText" dxfId="41" priority="75" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="76" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CB48">
+    <cfRule type="containsText" dxfId="39" priority="73" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="74" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DC55:DE55">
+    <cfRule type="containsText" dxfId="37" priority="67" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="68" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="XFD22">
+    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y20">
+    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",Y20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="34" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",Y20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z20">
+    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",Z20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",Z20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA20">
+    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AA20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AA20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB20">
+    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AB20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AB20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC20">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AC20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AC20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD20">
+    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AD20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AD20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE20">
     <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("y",AE20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W20:X20">
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="44" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF26:AJ26">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AF26)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AF26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="13" priority="41" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="42" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="11" priority="39" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="40" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DC55:DE55">
-    <cfRule type="containsText" dxfId="9" priority="33" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="34" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFD22">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AQ34">
+      <formula>NOT(ISERROR(SEARCH("x",AE20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF20">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AF20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AF20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG20">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AG20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AG20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG24">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AG24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG24">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AG24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH24">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AH24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH24">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AH24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH26">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AH26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH26">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AH26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AI26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI26">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AI26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ26">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AJ26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ26">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AJ26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK26">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AQ34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AQ34">
+      <formula>NOT(ISERROR(SEARCH("y",AK26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK26">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AQ34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AT36">
+      <formula>NOT(ISERROR(SEARCH("x",AK26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24">
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AT36)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AT36">
+      <formula>NOT(ISERROR(SEARCH("y",AI24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI24">
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AT36)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AU38">
+      <formula>NOT(ISERROR(SEARCH("x",AI24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ30">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AU38)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AU38">
+      <formula>NOT(ISERROR(SEARCH("y",AQ30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ30">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AU38)))</formula>
+      <formula>NOT(ISERROR(SEARCH("x",AQ30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/3_Documentazione/gant.xlsx
+++ b/3_Documentazione/gant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Cpt.local\shares\homes\allievi\SAM\IN\_folder-redir\jzl561\Desktop\git\cryptolan\3_Documentazione\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F135A1-D7E1-4922-A559-35C50A04AB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F61B7C-A0B0-44AE-BC59-FA5BA8D4C6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{1F676476-649A-4438-B998-67B3796BBA6E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="40">
   <si>
     <t>ATTIVITA</t>
   </si>
@@ -206,6 +206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -218,52 +219,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.39994506668294322"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4" tint="0.39994506668294322"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="58">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1189,138 +1149,138 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>45919</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4">
         <v>45926</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4">
         <v>45933</v>
       </c>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3">
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4">
         <v>45940</v>
       </c>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3">
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4">
         <v>45947</v>
       </c>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3">
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4"/>
+      <c r="AR1" s="4">
         <v>45954</v>
       </c>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
-      <c r="AZ1" s="3">
+      <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4">
         <v>45961</v>
       </c>
-      <c r="BA1" s="5"/>
-      <c r="BB1" s="5"/>
-      <c r="BC1" s="5"/>
-      <c r="BD1" s="5"/>
-      <c r="BE1" s="5"/>
-      <c r="BF1" s="5"/>
-      <c r="BG1" s="5"/>
-      <c r="BH1" s="3">
+      <c r="BA1" s="6"/>
+      <c r="BB1" s="6"/>
+      <c r="BC1" s="6"/>
+      <c r="BD1" s="6"/>
+      <c r="BE1" s="6"/>
+      <c r="BF1" s="6"/>
+      <c r="BG1" s="6"/>
+      <c r="BH1" s="4">
         <v>45975</v>
       </c>
-      <c r="BI1" s="5"/>
-      <c r="BJ1" s="5"/>
-      <c r="BK1" s="5"/>
-      <c r="BL1" s="5"/>
-      <c r="BM1" s="5"/>
-      <c r="BN1" s="5"/>
-      <c r="BO1" s="5"/>
-      <c r="BP1" s="3">
+      <c r="BI1" s="6"/>
+      <c r="BJ1" s="6"/>
+      <c r="BK1" s="6"/>
+      <c r="BL1" s="6"/>
+      <c r="BM1" s="6"/>
+      <c r="BN1" s="6"/>
+      <c r="BO1" s="6"/>
+      <c r="BP1" s="4">
         <v>45982</v>
       </c>
-      <c r="BQ1" s="5"/>
-      <c r="BR1" s="5"/>
-      <c r="BS1" s="5"/>
-      <c r="BT1" s="5"/>
-      <c r="BU1" s="5"/>
-      <c r="BV1" s="5"/>
-      <c r="BW1" s="5"/>
-      <c r="BX1" s="3">
+      <c r="BQ1" s="6"/>
+      <c r="BR1" s="6"/>
+      <c r="BS1" s="6"/>
+      <c r="BT1" s="6"/>
+      <c r="BU1" s="6"/>
+      <c r="BV1" s="6"/>
+      <c r="BW1" s="6"/>
+      <c r="BX1" s="4">
         <v>45989</v>
       </c>
-      <c r="BY1" s="5"/>
-      <c r="BZ1" s="5"/>
-      <c r="CA1" s="5"/>
-      <c r="CB1" s="5"/>
-      <c r="CC1" s="5"/>
-      <c r="CD1" s="5"/>
-      <c r="CE1" s="5"/>
-      <c r="CF1" s="3">
+      <c r="BY1" s="6"/>
+      <c r="BZ1" s="6"/>
+      <c r="CA1" s="6"/>
+      <c r="CB1" s="6"/>
+      <c r="CC1" s="6"/>
+      <c r="CD1" s="6"/>
+      <c r="CE1" s="6"/>
+      <c r="CF1" s="4">
         <v>45996</v>
       </c>
-      <c r="CG1" s="5"/>
-      <c r="CH1" s="5"/>
-      <c r="CI1" s="5"/>
-      <c r="CJ1" s="5"/>
-      <c r="CK1" s="5"/>
-      <c r="CL1" s="5"/>
-      <c r="CM1" s="5"/>
-      <c r="CN1" s="3">
+      <c r="CG1" s="6"/>
+      <c r="CH1" s="6"/>
+      <c r="CI1" s="6"/>
+      <c r="CJ1" s="6"/>
+      <c r="CK1" s="6"/>
+      <c r="CL1" s="6"/>
+      <c r="CM1" s="6"/>
+      <c r="CN1" s="4">
         <v>46003</v>
       </c>
-      <c r="CO1" s="5"/>
-      <c r="CP1" s="5"/>
-      <c r="CQ1" s="5"/>
-      <c r="CR1" s="5"/>
-      <c r="CS1" s="5"/>
-      <c r="CT1" s="5"/>
-      <c r="CU1" s="5"/>
-      <c r="CV1" s="5"/>
-      <c r="CW1" s="5">
+      <c r="CO1" s="6"/>
+      <c r="CP1" s="6"/>
+      <c r="CQ1" s="6"/>
+      <c r="CR1" s="6"/>
+      <c r="CS1" s="6"/>
+      <c r="CT1" s="6"/>
+      <c r="CU1" s="6"/>
+      <c r="CV1" s="6"/>
+      <c r="CW1" s="6">
         <v>19.12</v>
       </c>
-      <c r="CX1" s="5"/>
-      <c r="CY1" s="5"/>
-      <c r="CZ1" s="5"/>
-      <c r="DA1" s="5"/>
-      <c r="DB1" s="5"/>
-      <c r="DC1" s="5"/>
-      <c r="DD1" s="5"/>
-      <c r="DE1" s="5"/>
+      <c r="CX1" s="6"/>
+      <c r="CY1" s="6"/>
+      <c r="CZ1" s="6"/>
+      <c r="DA1" s="6"/>
+      <c r="DB1" s="6"/>
+      <c r="DC1" s="6"/>
+      <c r="DD1" s="6"/>
+      <c r="DE1" s="6"/>
     </row>
     <row r="2" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1652,7 +1612,7 @@
       </c>
     </row>
     <row r="3" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1667,7 +1627,7 @@
       </c>
     </row>
     <row r="4" spans="1:109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="5"/>
       <c r="C4">
         <f t="shared" ref="C4:C54" si="0">COUNTIFS(D4:CV4,"x")</f>
         <v>0</v>
@@ -1677,7 +1637,7 @@
       </c>
     </row>
     <row r="5" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1693,7 +1653,7 @@
       </c>
     </row>
     <row r="6" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="5"/>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1706,7 +1666,7 @@
       </c>
     </row>
     <row r="7" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -1722,7 +1682,7 @@
       </c>
     </row>
     <row r="8" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="5"/>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1735,7 +1695,7 @@
       </c>
     </row>
     <row r="9" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="5"/>
       <c r="B9" t="s">
         <v>37</v>
       </c>
@@ -1760,7 +1720,7 @@
       </c>
     </row>
     <row r="10" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="5"/>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1776,7 +1736,7 @@
       </c>
     </row>
     <row r="11" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
@@ -1818,7 +1778,7 @@
       </c>
     </row>
     <row r="12" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+      <c r="A12" s="7"/>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1837,7 +1797,7 @@
       </c>
     </row>
     <row r="13" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
+      <c r="A13" s="7"/>
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -1865,7 +1825,7 @@
       </c>
     </row>
     <row r="14" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1884,7 +1844,7 @@
       </c>
     </row>
     <row r="15" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" t="s">
         <v>12</v>
       </c>
@@ -1903,7 +1863,7 @@
       </c>
     </row>
     <row r="16" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1928,7 +1888,7 @@
       </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
+      <c r="A17" s="7"/>
       <c r="B17" t="s">
         <v>13</v>
       </c>
@@ -1962,7 +1922,7 @@
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+      <c r="A18" s="7"/>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1981,7 +1941,7 @@
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
+      <c r="A19" s="7"/>
       <c r="B19" t="s">
         <v>14</v>
       </c>
@@ -2015,7 +1975,7 @@
       </c>
     </row>
     <row r="20" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="7"/>
       <c r="C20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2034,7 +1994,7 @@
       <c r="BP20" s="1"/>
     </row>
     <row r="21" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
+      <c r="A21" s="7"/>
       <c r="B21" t="s">
         <v>15</v>
       </c>
@@ -2062,7 +2022,7 @@
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="C22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2090,7 +2050,7 @@
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
       <c r="B23" t="s">
         <v>16</v>
       </c>
@@ -2106,7 +2066,7 @@
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
+      <c r="A24" s="7"/>
       <c r="C24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2129,7 +2089,7 @@
       <c r="CJ24" s="1"/>
     </row>
     <row r="25" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
+      <c r="A25" s="7"/>
       <c r="B25" t="s">
         <v>34</v>
       </c>
@@ -2148,7 +2108,7 @@
       </c>
     </row>
     <row r="26" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
+      <c r="A26" s="7"/>
       <c r="C26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2164,7 +2124,7 @@
       </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
+      <c r="A27" s="7"/>
       <c r="B27" t="s">
         <v>17</v>
       </c>
@@ -2183,7 +2143,7 @@
       </c>
     </row>
     <row r="28" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
+      <c r="A28" s="7"/>
       <c r="C28">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2195,7 +2155,7 @@
       <c r="AL28" s="2"/>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
+      <c r="A29" s="7"/>
       <c r="B29" t="s">
         <v>18</v>
       </c>
@@ -2220,7 +2180,7 @@
       </c>
     </row>
     <row r="30" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
+      <c r="A30" s="7"/>
       <c r="C30">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2236,7 +2196,7 @@
       </c>
     </row>
     <row r="31" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
+      <c r="A31" s="7"/>
       <c r="B31" t="s">
         <v>19</v>
       </c>
@@ -2270,7 +2230,7 @@
       </c>
     </row>
     <row r="32" spans="1:88" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
+      <c r="A32" s="7"/>
       <c r="C32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2289,7 +2249,7 @@
       </c>
     </row>
     <row r="33" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
+      <c r="A33" s="7"/>
       <c r="B33" t="s">
         <v>20</v>
       </c>
@@ -2326,12 +2286,12 @@
       </c>
     </row>
     <row r="34" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
+      <c r="A34" s="7"/>
       <c r="C34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AR34" s="7"/>
+      <c r="AR34" s="3"/>
       <c r="AU34" t="s">
         <v>33</v>
       </c>
@@ -2353,13 +2313,13 @@
       <c r="BM34" t="s">
         <v>33</v>
       </c>
-      <c r="BN34" s="7"/>
+      <c r="BN34" s="3"/>
       <c r="BO34" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
+      <c r="A35" s="7"/>
       <c r="B35" t="s">
         <v>21</v>
       </c>
@@ -2378,7 +2338,7 @@
       </c>
     </row>
     <row r="36" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
+      <c r="A36" s="7"/>
       <c r="C36">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2394,7 +2354,7 @@
       </c>
     </row>
     <row r="37" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
+      <c r="A37" s="7"/>
       <c r="B37" t="s">
         <v>22</v>
       </c>
@@ -2437,7 +2397,7 @@
       </c>
     </row>
     <row r="38" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
+      <c r="A38" s="7"/>
       <c r="C38">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2492,7 +2452,7 @@
       </c>
     </row>
     <row r="39" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
+      <c r="A39" s="7"/>
       <c r="B39" t="s">
         <v>23</v>
       </c>
@@ -2526,7 +2486,7 @@
       </c>
     </row>
     <row r="40" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B40" t="s">
@@ -2547,14 +2507,14 @@
       </c>
     </row>
     <row r="41" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
+      <c r="A41" s="5"/>
       <c r="C41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="5"/>
       <c r="B42" t="s">
         <v>26</v>
       </c>
@@ -2570,14 +2530,14 @@
       </c>
     </row>
     <row r="43" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
+      <c r="A43" s="5"/>
       <c r="C43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="5"/>
       <c r="B44" t="s">
         <v>27</v>
       </c>
@@ -2590,14 +2550,14 @@
       </c>
     </row>
     <row r="45" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="5"/>
       <c r="C45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="5"/>
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -2613,14 +2573,14 @@
       </c>
     </row>
     <row r="47" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="5"/>
       <c r="C47">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:89" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="5"/>
       <c r="B48" t="s">
         <v>28</v>
       </c>
@@ -2636,14 +2596,23 @@
       </c>
     </row>
     <row r="49" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="5"/>
       <c r="C49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="BS49" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT49" t="s">
+        <v>33</v>
+      </c>
+      <c r="BU49" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="50" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="5"/>
       <c r="B50" t="s">
         <v>29</v>
       </c>
@@ -2659,14 +2628,14 @@
       </c>
     </row>
     <row r="51" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="5"/>
       <c r="C51">
         <f>COUNTIFS(D51:CV51,"x")</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="5"/>
       <c r="B52" t="s">
         <v>30</v>
       </c>
@@ -2677,6 +2646,33 @@
       <c r="N52" t="s">
         <v>32</v>
       </c>
+      <c r="BV52" t="s">
+        <v>33</v>
+      </c>
+      <c r="BW52" t="s">
+        <v>33</v>
+      </c>
+      <c r="BX52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CA52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CB52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CC52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CD52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CE52" t="s">
+        <v>33</v>
+      </c>
+      <c r="CI52" t="s">
+        <v>33</v>
+      </c>
       <c r="CN52" t="s">
         <v>8</v>
       </c>
@@ -2703,7 +2699,7 @@
       </c>
     </row>
     <row r="53" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
@@ -2766,14 +2762,35 @@
       </c>
     </row>
     <row r="54" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="5"/>
       <c r="C54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="CA54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CB54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CI54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CJ54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CK54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CL54" t="s">
+        <v>33</v>
+      </c>
+      <c r="CM54" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="55" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B55" t="s">
@@ -2794,15 +2811,10 @@
       </c>
     </row>
     <row r="56" spans="1:109" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="L1:S1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="A40:A52"/>
-    <mergeCell ref="A53:A54"/>
     <mergeCell ref="CW1:DE1"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="CF1:CM1"/>
@@ -2816,271 +2828,270 @@
     <mergeCell ref="BP1:BW1"/>
     <mergeCell ref="BX1:CE1"/>
     <mergeCell ref="D1:K1"/>
+    <mergeCell ref="L1:S1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="A40:A52"/>
+    <mergeCell ref="A53:A54"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 P15:P39 N16:O16 Y17:CV17 M17:O40 S17:S40 Y23:AF25 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AV33:BA33 BD33:CV33 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C54:CV543 BF38:BJ38 Y19:CV19 Z18:CV18 AH20:CV20 AL23:CV26 Y21:CV22 S15:CV16 AU34:CV34 AR29:AS39">
-    <cfRule type="containsText" dxfId="61" priority="79" operator="containsText" text="y">
+  <conditionalFormatting sqref="C3:CV10 P11:AM11 AU11:CV11 M11:O15 C11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 M17:O40 S17:S40 Y19:CV19 Y21:CV22 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AU34:CV34 BN35:CV38 AV35:BE39 BF38:BJ38 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CN52:CW52 CY52:DB52 C53:CB53 CV53:DB53 C56:CV543 C55:CK55 C54:BZ54 CC54:CK54 CM55:CV55 CN54:CV54">
+    <cfRule type="containsText" dxfId="57" priority="105" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 P15:P39 N16:O16 Y17:CV17 M17:O40 S17:S40 Y23:AF25 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AV33:BA33 BD33:CV33 BN35:CV38 AV35:BE39 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CC52 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53 BF38:BJ38 Y19:CV19 Z18:CV18 AH20:CV20 AL23:CV26 Y21:CV22 S15:CV16 AU34:CV34 AR29:AS39">
-    <cfRule type="containsText" dxfId="60" priority="80" operator="containsText" text="x">
+  <conditionalFormatting sqref="D3:CV10 P11:AM11 AU11:CV11 M11:O15 D11:I52 P12:CV14 S15:CV16 P15:P39 N16:O16 M17:O40 S17:S40 Y19:CV19 Y21:CV22 Y23:AF25 AL23:CV26 Y26:AD26 AR27:CV28 Y27:AF39 AL27:AP39 AI28:AK28 AV29:CV32 AR29:AS39 AV33:BA33 BD33:CV33 AU34:CV34 BN35:CV38 AV35:BE39 BF38:BJ38 BN39:BY39 CD39:CV39 V40:CV40 M41:CV41 AG42:CV42 M42:AA52 AE43:CV43 AE44:AK44 AM44:AO44 AQ44:CV44 AE45:CV45 AE46:BB46 BH46:CV46 AE47:CV47 AE48:BI48 BM48:BO48 BS48:BZ48 CC48:CV49 AE49:CA49 CD50:CV50 AE50:BP52 CC51:CV51 CN52:CW52 CY52:DB52 D53:CB53 CV53:DB53">
+    <cfRule type="containsText" dxfId="56" priority="106" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12:L12">
-    <cfRule type="containsText" dxfId="59" priority="63" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="55" priority="89" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",K12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="64" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="54" priority="90" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",K12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q16:R16">
-    <cfRule type="containsText" dxfId="57" priority="61" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="53" priority="87" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",Q16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="62" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="52" priority="88" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",Q16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T18:Y18">
-    <cfRule type="containsText" dxfId="55" priority="55" operator="containsText" text="y">
+  <conditionalFormatting sqref="T18:CV18">
+    <cfRule type="containsText" dxfId="51" priority="81" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",T18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="56" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="50" priority="82" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",T18)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W20:X20">
-    <cfRule type="containsText" dxfId="53" priority="51" operator="containsText" text="y">
+  <conditionalFormatting sqref="W20:CV20">
+    <cfRule type="containsText" dxfId="49" priority="43" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",W20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="52" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="48" priority="44" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",W20)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X17">
-    <cfRule type="containsText" dxfId="51" priority="77" operator="containsText" text="y">
+  <conditionalFormatting sqref="X17:CV17">
+    <cfRule type="containsText" dxfId="47" priority="103" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",X17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="78" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="46" priority="104" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",X17)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF26:AG26">
-    <cfRule type="containsText" dxfId="49" priority="41" operator="containsText" text="y">
+  <conditionalFormatting sqref="AF26:AK26">
+    <cfRule type="containsText" dxfId="45" priority="31" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",AF26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="42" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="44" priority="32" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",AF26)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AG24:AI24">
+    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AG24)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="30" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AG24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ30">
+    <cfRule type="containsText" dxfId="41" priority="27" operator="containsText" text="y">
+      <formula>NOT(ISERROR(SEARCH("y",AQ30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="28" operator="containsText" text="x">
+      <formula>NOT(ISERROR(SEARCH("x",AQ30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AQ34">
-    <cfRule type="containsText" dxfId="47" priority="39" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="39" priority="65" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",AQ34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="40" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="38" priority="66" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",AQ34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AT36">
-    <cfRule type="containsText" dxfId="45" priority="37" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="37" priority="63" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",AT36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="38" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="36" priority="64" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",AT36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AU38">
-    <cfRule type="containsText" dxfId="43" priority="35" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="35" priority="61" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",AU38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="36" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="34" priority="62" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",AU38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM35">
-    <cfRule type="containsText" dxfId="41" priority="75" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="33" priority="101" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",BM35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="76" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="32" priority="102" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",BM35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CB48">
-    <cfRule type="containsText" dxfId="39" priority="73" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="31" priority="99" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",CB48)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="74" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="30" priority="100" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",CB48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DC55:DE55">
-    <cfRule type="containsText" dxfId="37" priority="67" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="29" priority="93" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",DC55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="68" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="28" priority="94" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",DC55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="XFD22">
-    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="y">
+    <cfRule type="containsText" dxfId="27" priority="75" operator="containsText" text="y">
       <formula>NOT(ISERROR(SEARCH("y",XFD22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="x">
+    <cfRule type="containsText" dxfId="26" priority="76" operator="containsText" text="x">
       <formula>NOT(ISERROR(SEARCH("x",XFD22)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y20">
-    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",Y20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="34" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",Y20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20">
-    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",Z20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",Z20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA20">
-    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AA20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AA20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB20">
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AB20)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AB20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC20">
+  <conditionalFormatting sqref="BV52">
     <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AC20)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",BV52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BV52">
     <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AC20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD20">
+      <formula>NOT(ISERROR(SEARCH("x",BV52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW52">
     <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AD20)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",BW52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW52">
     <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AD20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE20">
+      <formula>NOT(ISERROR(SEARCH("x",BW52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX52">
     <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AE20)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",BX52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BX52">
     <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AE20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF20">
+      <formula>NOT(ISERROR(SEARCH("x",BX52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CA52">
     <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AF20)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",CA52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CA52">
     <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AF20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG20">
+      <formula>NOT(ISERROR(SEARCH("x",CA52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CB52">
     <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AG20)))</formula>
-    </cfRule>
+      <formula>NOT(ISERROR(SEARCH("y",CB52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CB52">
     <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AG20)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG24">
+      <formula>NOT(ISERROR(SEARCH("x",CB52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CC52">
     <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AG24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG24">
+      <formula>NOT(ISERROR(SEARCH("y",CC52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CC52">
     <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AG24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH24">
+      <formula>NOT(ISERROR(SEARCH("x",CC52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CB54">
     <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AH24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH24">
+      <formula>NOT(ISERROR(SEARCH("y",CB54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CB54">
     <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AH24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH26">
+      <formula>NOT(ISERROR(SEARCH("x",CB54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CA54">
     <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AH26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH26">
+      <formula>NOT(ISERROR(SEARCH("y",CA54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CA54">
     <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AH26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI26">
+      <formula>NOT(ISERROR(SEARCH("x",CA54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CD52">
     <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AI26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI26">
+      <formula>NOT(ISERROR(SEARCH("y",CD52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CD52">
     <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AI26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ26">
+      <formula>NOT(ISERROR(SEARCH("x",CD52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CE52">
     <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AJ26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ26">
+      <formula>NOT(ISERROR(SEARCH("y",CE52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CE52">
     <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AJ26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK26">
+      <formula>NOT(ISERROR(SEARCH("x",CE52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CL54">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AK26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK26">
+      <formula>NOT(ISERROR(SEARCH("y",CL54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CL54">
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AK26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI24">
+      <formula>NOT(ISERROR(SEARCH("x",CL54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CM54">
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AI24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI24">
+      <formula>NOT(ISERROR(SEARCH("y",CM54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CM54">
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AI24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AQ30">
+      <formula>NOT(ISERROR(SEARCH("x",CM54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CI52">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="y">
-      <formula>NOT(ISERROR(SEARCH("y",AQ30)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AQ30">
+      <formula>NOT(ISERROR(SEARCH("y",CI52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CI52">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="x">
-      <formula>NOT(ISERROR(SEARCH("x",AQ30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("x",CI52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
